--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,40 +633,40 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
         <v>7</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W2" t="n">
         <v>8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>12</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -740,7 +883,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: L. Muhammad (16 L)</t>
+          <t>Maior volume: J. Slater (25 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +895,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: L. Muhammad (5 3PA)</t>
+          <t>Maior volume 3pt: J. Slater (9 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +907,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: J. Slater (1.5 pts/shot)</t>
+          <t>Mais eficaz: L. Barrett (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +919,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (20 L)</t>
+          <t>Zona mais usada: Restricted Area (36 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +931,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (65.0%)</t>
+          <t>Zona mais eficaz: Restricted Area (77.8%)</t>
         </is>
       </c>
     </row>
@@ -928,68 +1071,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>7</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1005,55 +1148,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1062,18 +1205,18 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1091,123 +1234,123 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1216,7 +1359,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1224,265 +1367,269 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_D._RELVAO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>D. Relvao</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_L._SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>L. Silva</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1490,33 +1637,33 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1524,17 +1671,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1549,13 +1696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1727,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1597,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1612,11 +1759,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -1736,42 +1883,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1780,45 +1927,45 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1830,25 +1977,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1857,20 +2004,20 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1890,68 +2037,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="n">
         <v>9</v>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1964,8 +2111,239 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2070,50 +2448,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2126,50 +2504,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2182,150 +2560,150 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
         <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
         <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2333,89 +2711,89 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_D._RELVAO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>D. Relvao</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2427,25 +2805,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -2453,7 +2831,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
         <v>6</v>
@@ -2462,52 +2840,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_L._SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>L. Silva</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="M9" t="n">
-        <v>8</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2533,10 +2917,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -2547,7 +2931,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2555,7 +2939,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -2671,25 +3055,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2702,106 +3086,106 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2811,7 +3195,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -2821,11 +3205,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2836,7 +3220,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2846,32 +3230,32 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2992,141 +3376,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -3142,212 +3526,212 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3356,152 +3740,156 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_D._RELVAO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>D. Relvao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_L._SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>L. Silva</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3509,12 +3897,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -3526,11 +3914,11 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -3538,11 +3926,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3562,7 +3950,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3576,7 +3964,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3603,11 +3991,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3693,7 +4081,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3711,14 +4099,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3738,25 +4126,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3769,50 +4157,455 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -629,35 +629,35 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>58</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>36</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
         <v>4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>7</v>
       </c>
       <c r="U2" t="n">
         <v>7</v>
@@ -666,7 +666,7 @@
         <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -681,12 +681,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -802,50 +802,365 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>L. Muhammad</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>36.7%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>41.7%</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -883,7 +1198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: J. Slater (25 L)</t>
+          <t>Maior volume: J. Slater (38 L)</t>
         </is>
       </c>
     </row>
@@ -895,7 +1210,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: J. Slater (9 3PA)</t>
+          <t>Maior volume 3pt: J. Slater (12 3PA)</t>
         </is>
       </c>
     </row>
@@ -919,7 +1234,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (36 L)</t>
+          <t>Zona mais usada: Above the Break 3 (58 L)</t>
         </is>
       </c>
     </row>
@@ -931,7 +1246,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (77.8%)</t>
+          <t>Zona mais eficaz: Restricted Area (78.9%)</t>
         </is>
       </c>
     </row>
@@ -947,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1080,30 +1395,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1115,11 +1430,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1128,11 +1443,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1157,34 +1472,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1192,34 +1507,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1234,30 +1549,30 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1265,28 +1580,28 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1296,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1311,34 +1626,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>11</v>
       </c>
-      <c r="E5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1346,11 +1661,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1359,18 +1674,18 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1388,34 +1703,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1423,24 +1738,24 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1450,7 +1765,7 @@
         <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1465,34 +1780,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1500,34 +1815,34 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1542,69 +1857,69 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1619,7 +1934,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1633,7 +1948,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1642,7 +1957,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1650,24 +1965,24 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1678,10 +1993,10 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1696,47 +2011,61 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
@@ -1744,11 +2073,242 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SLB_J._ANDRADE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Andrade</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1759,7 +2319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1896,55 +2456,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1954,53 +2514,53 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
         <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -2008,7 +2568,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2017,21 +2577,21 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2050,42 +2610,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G4" t="n">
+        <v>45</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>13</v>
       </c>
-      <c r="G4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>36.0%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2094,11 +2654,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2108,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2123,33 +2683,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2158,24 +2718,24 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -2191,12 +2751,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_D._RELVAO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>D. Relvao</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2204,29 +2764,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2244,7 +2804,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -2252,98 +2812,252 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
+        <v>28</v>
+      </c>
+      <c r="H7" t="n">
         <v>11</v>
       </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
-        <v>5</v>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>36</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SLB_L._SILVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L. Silva</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2354,7 +3068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2457,26 +3171,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -2487,18 +3201,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2513,29 +3227,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2543,18 +3257,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2569,29 +3283,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2599,15 +3313,15 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
@@ -2616,42 +3330,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2659,85 +3373,85 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
         <v>7</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_L._SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>L. Silva</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2749,129 +3463,129 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_D._RELVAO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>D. Relvao</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2879,55 +3593,59 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB_E._FRANCISCO</t>
+          <t>SLB_J._ANDRADE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E. Francisco</t>
+          <t>J. Andrade</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2935,16 +3653,186 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SLB_E._FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>E. Francisco</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>9</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2955,28 +3843,267 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>36.7%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3051,71 +4178,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3125,17 +4252,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3143,7 +4270,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3160,25 +4287,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3195,32 +4322,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3230,13 +4357,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3248,7 +4375,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3270,7 +4397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3390,11 +4517,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3403,40 +4530,40 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>7</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3460,57 +4587,57 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -3526,28 +4653,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3556,27 +4683,27 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -3600,57 +4727,57 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>57.1%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -3670,57 +4797,57 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3740,24 +4867,24 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3766,31 +4893,31 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8">
@@ -3806,61 +4933,61 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3876,53 +5003,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -3950,37 +5077,251 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SLB_J._ANDRADE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Andrade</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3991,7 +5332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4081,21 +5422,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4126,17 +5467,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4144,7 +5485,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4157,84 +5498,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4247,102 +5588,102 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
         <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>31.8%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4351,70 +5692,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -4427,57 +5768,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4486,29 +5827,29 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -4517,39 +5858,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -4562,50 +5903,320 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>18.4%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>SLB_G._CRANDALL</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>G. Crandall</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
@@ -24,11 +24,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -629,44 +629,44 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>86</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>75.6%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>58</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>24.1%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="n">
         <v>13</v>
       </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,17 +816,17 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -834,11 +834,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -847,84 +847,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -937,133 +937,133 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -1072,95 +1072,410 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14.5%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>L. Muhammad</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>36.0%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>24.0%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1198,7 +1513,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: J. Slater (38 L)</t>
+          <t>Maior volume: J. Slater (55 L)</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1525,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: J. Slater (12 3PA)</t>
+          <t>Maior volume 3pt: A. Broussard (15 3PA)</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1537,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: L. Barrett (1.3 pts/shot)</t>
+          <t>Mais eficaz: A. Dziewa (1.4 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1549,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (58 L)</t>
+          <t>Zona mais usada: Restricted Area (86 L)</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1561,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (78.9%)</t>
+          <t>Zona mais eficaz: Restricted Area (75.6%)</t>
         </is>
       </c>
     </row>
@@ -1395,59 +1710,59 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>22</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>31.6%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>10</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1472,30 +1787,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1507,24 +1822,24 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1534,7 +1849,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1549,30 +1864,30 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1580,38 +1895,38 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1626,30 +1941,30 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1661,16 +1976,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1678,17 +1993,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
         <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1703,34 +2018,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1738,31 +2053,31 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>6</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1780,34 +2095,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1815,31 +2130,31 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>7</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1857,30 +2172,30 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1901,25 +2216,25 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1934,34 +2249,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1969,24 +2284,24 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1996,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -2011,43 +2326,43 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>100.0%</t>
@@ -2055,15 +2370,15 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -2073,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2088,7 +2403,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -2098,11 +2413,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2111,11 +2426,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -2123,34 +2438,34 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2227,7 +2542,7 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -2301,7 +2616,7 @@
         <v>11</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S13" t="n">
         <v>12</v>
@@ -2443,47 +2758,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -2491,41 +2806,41 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2533,29 +2848,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2564,11 +2879,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2577,21 +2892,21 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2606,59 +2921,59 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>22</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>31.6%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2674,12 +2989,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_D._RELVAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>D. Relvao</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2687,142 +3002,142 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="E6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="n">
         <v>13</v>
       </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2841,29 +3156,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2872,16 +3187,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -2889,17 +3204,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2918,29 +3233,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2949,24 +3264,24 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -2991,33 +3306,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3026,24 +3341,24 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -3162,113 +3477,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3283,29 +3598,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3313,11 +3628,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -3330,262 +3645,262 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>26.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" t="n">
-        <v>39</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_L._SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>L. Silva</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
         <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>36</v>
-      </c>
-      <c r="H6" t="n">
-        <v>21</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>15</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_E._FRANCISCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>E. Francisco</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H8" t="n">
-        <v>23</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3593,18 +3908,18 @@
         </is>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
         <v>5</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3619,7 +3934,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -3631,17 +3946,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3649,7 +3964,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -3657,66 +3972,66 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLB_E._FRANCISCO</t>
+          <t>SLB_D._RELVAO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E. Francisco</t>
+          <t>D. Relvao</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3769,7 +4084,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -3828,7 +4143,7 @@
         <v>12</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3843,7 +4158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3946,26 +4261,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I2" t="n">
         <v>0.9</v>
@@ -3976,18 +4291,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -4002,29 +4317,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4032,11 +4347,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4058,29 +4373,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4088,11 +4403,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4102,8 +4417,120 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>26.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SLB_L._SILVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Silva</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4178,71 +4605,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -4252,17 +4679,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4270,7 +4697,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4287,32 +4714,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4322,7 +4749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -4332,22 +4759,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -4357,7 +4784,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -4367,11 +4794,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4382,7 +4809,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4517,11 +4944,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4530,44 +4957,44 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>55</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>55.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>12</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3">
@@ -4587,53 +5014,53 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -4653,28 +5080,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4691,19 +5118,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -4727,16 +5154,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4744,36 +5171,36 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>37.5%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -4797,24 +5224,24 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4831,23 +5258,23 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -4867,57 +5294,57 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
@@ -4946,20 +5373,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -4967,23 +5394,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -5007,29 +5434,29 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -5041,23 +5468,23 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
@@ -5077,7 +5504,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5086,48 +5513,48 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>5</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -5147,57 +5574,57 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -5332,7 +5759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5408,271 +5835,271 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -5688,78 +6115,78 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -5768,57 +6195,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5827,7 +6254,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -5837,19 +6264,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -5858,57 +6285,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5917,7 +6344,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -5927,19 +6354,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -5948,57 +6375,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6007,7 +6434,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -6017,15 +6444,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -6052,171 +6479,396 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SLB_L._SILVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>L. Silva</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K19"/>
+  <autoFilter ref="A1:K24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>